--- a/ai_logs/PhanVanBao_ai_log.xlsx
+++ b/ai_logs/PhanVanBao_ai_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\NHOM_04_LAB211_TicketBooking\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4785C881-EFC0-4B7C-BBE0-4A71F08EEABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D23EAD-5E75-4AAA-83F6-9F240316BA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="162">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -526,6 +526,9 @@
   </si>
   <si>
     <t>Full code DataGenerator.java + ảnh terminal “✅ Đã tạo dữ liệu CSV đầy đủ!”.</t>
+  </si>
+  <si>
+    <t>hh</t>
   </si>
 </sst>
 </file>
@@ -702,12 +705,12 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1031,7 +1034,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="19"/>
@@ -1270,7 +1273,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>41</v>
       </c>
       <c r="B1" s="19"/>
@@ -1282,7 +1285,7 @@
       <c r="H1" s="19"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="18" t="s">
         <v>42</v>
       </c>
       <c r="B2" s="19"/>
@@ -1505,7 +1508,9 @@
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
+      <c r="D11" s="7" t="s">
+        <v>161</v>
+      </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1994,7 +1999,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>104</v>
       </c>
       <c r="B1" s="19"/>

--- a/ai_logs/PhanVanBao_ai_log.xlsx
+++ b/ai_logs/PhanVanBao_ai_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\NHOM_04_LAB211_TicketBooking\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D23EAD-5E75-4AAA-83F6-9F240316BA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACE27B2-46C1-4EE2-A613-400BB78FE677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3036" yWindow="3036" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="163">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -529,6 +529,9 @@
   </si>
   <si>
     <t>hh</t>
+  </si>
+  <si>
+    <t>cccccccc</t>
   </si>
 </sst>
 </file>
@@ -1511,7 +1514,9 @@
       <c r="D11" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E11" s="7"/>
+      <c r="E11" s="7" t="s">
+        <v>162</v>
+      </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>

--- a/ai_logs/PhanVanBao_ai_log.xlsx
+++ b/ai_logs/PhanVanBao_ai_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\NHOM_04_LAB211_TicketBooking\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACE27B2-46C1-4EE2-A613-400BB78FE677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FB4568-87C4-4E5A-B5FA-89078E2DBE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3036" yWindow="3036" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="161">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -526,12 +526,6 @@
   </si>
   <si>
     <t>Full code DataGenerator.java + ảnh terminal “✅ Đã tạo dữ liệu CSV đầy đủ!”.</t>
-  </si>
-  <si>
-    <t>hh</t>
-  </si>
-  <si>
-    <t>cccccccc</t>
   </si>
 </sst>
 </file>
@@ -1511,12 +1505,8 @@
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>162</v>
-      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>

--- a/ai_logs/PhanVanBao_ai_log.xlsx
+++ b/ai_logs/PhanVanBao_ai_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\NHOM_04_LAB211_TicketBooking\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FB4568-87C4-4E5A-B5FA-89078E2DBE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD1713A1-8096-49A0-8EF0-91DEF97FB1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <sheet name="4. Self-Assessment Checklist" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="174">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -195,75 +196,15 @@
     <t>DECISION</t>
   </si>
   <si>
-    <t>Cần chia nhỏ requirement</t>
-  </si>
-  <si>
-    <t>Break down student management into modules</t>
-  </si>
-  <si>
-    <t>AI suggested 10 modules: User, Student, Course, Grade, Attendance, Report, Export, Import, Settings, Dashboard</t>
-  </si>
-  <si>
-    <t>Critical Thinking: 10 modules quá nhiều cho project 300 LOC.
-Contextualization: Project scope nhỏ, chỉ cần core functions.
-Creative Synthesis: Tôi gộp thành 5 modules: Student, Grade, File I/O, Validation, UI.
-Decision: Chọn 5 modules vì đủ để implement requirements mà không phức tạp.</t>
-  </si>
-  <si>
-    <t>Screenshot comparison 10 vs 5</t>
-  </si>
-  <si>
     <t>002</t>
   </si>
   <si>
     <t>PROBLEM-SOLVING</t>
   </si>
   <si>
-    <t>Search by name quá chậm với 10K records</t>
-  </si>
-  <si>
-    <t>How to optimize search for player name in 10,000 records?</t>
-  </si>
-  <si>
-    <t>AI suggested Binary Search with O(log n) complexity</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Binary Search cần sort trước → O(n log n). Với partial match không phù hợp.
-Contextualization: Requirements yêu cầu partial name search.
-Creative Synthesis: Test 3 approaches: Binary Search, Linear Search, HashMap. HashMap fastest (2ms).
-Decision: Chọn HashMap trade-off memory cho speed.</t>
-  </si>
-  <si>
-    <t>Code snippet + timing comparison</t>
-  </si>
-  <si>
     <t>003</t>
   </si>
   <si>
-    <t>VERIFICATION</t>
-  </si>
-  <si>
-    <t>Literature Review</t>
-  </si>
-  <si>
-    <t>Cần verify paper AI cite</t>
-  </si>
-  <si>
-    <t>Is the paper 'Smith et al. 2023 on IoT anomaly detection' a real publication?</t>
-  </si>
-  <si>
-    <t>AI confirmed it exists and provided summary</t>
-  </si>
-  <si>
-    <t>Critical Thinking: HALLUCINATION DETECTED! Search Google Scholar → paper NOT FOUND.
-Contextualization: AI fabricated paper to answer my question.
-Creative Synthesis: Found real paper 'Jones et al. 2022' with similar topic.
-Decision: Replace with verified paper from Google Scholar.</t>
-  </si>
-  <si>
-    <t>Google Scholar screenshot</t>
-  </si>
-  <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
   </si>
   <si>
@@ -291,18 +232,6 @@
     <t>Fabrication</t>
   </si>
   <si>
-    <t>Paper 'Smith et al. 2023' exists</t>
-  </si>
-  <si>
-    <t>Paper NOT FOUND on Google Scholar</t>
-  </si>
-  <si>
-    <t>Searched Google Scholar, ResearchGate</t>
-  </si>
-  <si>
-    <t>Used real paper 'Jones et al. 2022'</t>
-  </si>
-  <si>
     <t>HALLUCINATION TYPES REFERENCE:</t>
   </si>
   <si>
@@ -526,6 +455,108 @@
   </si>
   <si>
     <t>Full code DataGenerator.java + ảnh terminal “✅ Đã tạo dữ liệu CSV đầy đủ!”.</t>
+  </si>
+  <si>
+    <t>Cần chia nhỏ luồng đặt vé thành các bước rõ ràng</t>
+  </si>
+  <si>
+    <t>“Hãy phân tích flow đặt vé từ lúc fan chọn ghế đến khi ghi vào file CSV”</t>
+  </si>
+  <si>
+    <t>AI gợi ý 6 bước: chọn ghế, kiểm tra trạng thái, lock ghế, tạo vé, ghi transaction, confirm</t>
+  </si>
+  <si>
+    <t>Critical Thinking: 6 bước hợp lý nhưng hơi chi tiết. Contextualization: Với scope lab, chỉ cần 4 bước chính. Creative Synthesis: Gộp thành: chọn ghế → lock → ghi vé → ghi transaction. Decision: Giữ 4 bước để flowchart đơn giản.</t>
+  </si>
+  <si>
+    <t>Flowchart Booking Flow (draw.io)</t>
+  </si>
+  <si>
+    <t>Code snippet FileLock + kết quả test</t>
+  </si>
+  <si>
+    <t>Critical Thinking: synchronized chưa đủ khi nhiều file CSV. Contextualization: Phải đảm bảo atomic write. Creative Synthesis: Thử FileLock và Optimistic Locking. Decision: Chọn FileLock cho seats.csv.</t>
+  </si>
+  <si>
+    <t>AI gợi ý dùng synchronized block</t>
+  </si>
+  <si>
+    <t>“Làm sao để ngăn double booking khi chạy 100 threads?”</t>
+  </si>
+  <si>
+    <t>Simulator chạy 100 threads vẫn bị double booking</t>
+  </si>
+  <si>
+    <t>AI nói số lượng vé có thể nhiều hơn số lượng ghế</t>
+  </si>
+  <si>
+    <t>Thực tế vé phải ≤ seats × matches</t>
+  </si>
+  <si>
+    <t>Kiểm tra capacity stadium và logic nghiệp vụ</t>
+  </si>
+  <si>
+    <t>Sửa DataGenerator để sinh tickets theo capacity stadium</t>
+  </si>
+  <si>
+    <t>AI giữ cột status trong transactions.csv</t>
+  </si>
+  <si>
+    <t>Thực tế không cần status vì giao dịch chỉ ghi thông tin vé</t>
+  </si>
+  <si>
+    <t>Đọc lại yêu cầu nghiệp vụ trong đề tài</t>
+  </si>
+  <si>
+    <t>Bỏ cột status, giữ schema đơn giản</t>
+  </si>
+  <si>
+    <t>AI nói chỉ cần ticketType = VIP/NORMAL là đủ</t>
+  </si>
+  <si>
+    <t>Thực tế còn phải mapping từ sections.csv và tín h giá vé khác nhau</t>
+  </si>
+  <si>
+    <t>Kiểm tra dữ liệu sections.csv và yêu cầu business</t>
+  </si>
+  <si>
+    <t>Bổ sung logic giá vé theo loại khu vực</t>
+  </si>
+  <si>
+    <t>AI gợi ý dùng Thread.stop() để dừng simulator</t>
+  </si>
+  <si>
+    <t>Phương thức này deprecated từ Java 8</t>
+  </si>
+  <si>
+    <t>Đọc tài liệu JavaDoc chính thức</t>
+  </si>
+  <si>
+    <t>Dùng ExecutorService.shutdown() thay thế</t>
+  </si>
+  <si>
+    <t>AI nói synchronized block đủ để ngăn double booking</t>
+  </si>
+  <si>
+    <t>Thực tế vẫn xảy ra double booking với 100 threads</t>
+  </si>
+  <si>
+    <t>Chạy simulator 100 threads</t>
+  </si>
+  <si>
+    <t>Thêm cơ chế FileLock để đảm bảo atomic write</t>
+  </si>
+  <si>
+    <t>AI khẳng định Optimistic Locking cho CSV đã có nghiên cứu chính thức</t>
+  </si>
+  <si>
+    <t>Không tìm thấy paper nào về CSV Optimistic Locking</t>
+  </si>
+  <si>
+    <t>Tìm trên Google Scholar</t>
+  </si>
+  <si>
+    <t>Tự kiểm chứng bằng simulator, giữ version field như giải pháp thực nghiệm</t>
   </si>
 </sst>
 </file>
@@ -665,7 +696,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -718,6 +749,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1050,7 +1082,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1058,7 +1090,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1066,7 +1098,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1074,7 +1106,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1262,10 +1294,10 @@
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="4" max="4" width="40.88671875" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="35" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
+    <col min="7" max="7" width="82.33203125" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1319,9 +1351,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>51</v>
+    <row r="4" spans="1:8" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7">
+        <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>52</v>
@@ -1330,71 +1362,71 @@
         <v>36</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="E4" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7">
+        <v>2</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>59</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>60</v>
+      <c r="D5" t="s">
+        <v>135</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>63</v>
+        <v>137</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>138</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>65</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7">
+        <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>68</v>
+        <v>149</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>69</v>
+        <v>148</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>71</v>
+        <v>146</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1402,25 +1434,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>40</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1434,19 +1466,19 @@
         <v>39</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1460,46 +1492,30 @@
         <v>38</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7">
-        <v>7</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>160</v>
-      </c>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
@@ -1667,6 +1683,7 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1682,7 +1699,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1692,7 +1709,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -1702,85 +1719,143 @@
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7">
+        <v>2</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
+      <c r="C7" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="A8" s="7">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="A9" s="7">
+        <v>6</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
@@ -1904,73 +1979,73 @@
     </row>
     <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1995,7 +2070,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -2003,7 +2078,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -2011,185 +2086,185 @@
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="D10" s="13"/>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -2197,13 +2272,13 @@
         <v>43</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -2216,7 +2291,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -2224,7 +2299,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>

--- a/ai_logs/PhanVanBao_ai_log.xlsx
+++ b/ai_logs/PhanVanBao_ai_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\NHOM_04_LAB211_TicketBooking\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD1713A1-8096-49A0-8EF0-91DEF97FB1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E51B5D-FF5E-410E-B891-41B866E7173D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <sheet name="4. Self-Assessment Checklist" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="222">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -557,6 +556,183 @@
   </si>
   <si>
     <t>Tự kiểm chứng bằng simulator, giữ version field như giải pháp thực nghiệm</t>
+  </si>
+  <si>
+    <t>SCHEMA EXTENSION</t>
+  </si>
+  <si>
+    <t>Schema Extension</t>
+  </si>
+  <si>
+    <t>StadiumId</t>
+  </si>
+  <si>
+    <t>“Có thấy stadiumId không?”</t>
+  </si>
+  <si>
+    <t>AI giải thích hiện chưa có stadiumId, gợi ý thêm vào Ticket.java và CSV.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Nhận ra cần mở rộng schema để quản lý vé theo sân. Decision: Thêm stadiumId vào Ticket.java và cập nhật CSV.</t>
+  </si>
+  <si>
+    <t>Code Ticket.java (bản mở rộng)</t>
+  </si>
+  <si>
+    <t>UNIT TESTING</t>
+  </si>
+  <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>Kiểm tra dữ liệu CSV</t>
+  </si>
+  <si>
+    <t>“Phân tích từng dòng code TicketCsvTest.”</t>
+  </si>
+  <si>
+    <t>AI phân tích chi tiết từng dòng: đọc file, bỏ qua header, kiểm tra số cột, ô trống.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Xác nhận test này dùng để validate dữ liệu, không phải nghiệp vụ. Decision: Giữ test để đảm bảo file CSV sạch.</t>
+  </si>
+  <si>
+    <t>Code TicketCsvTest + output console</t>
+  </si>
+  <si>
+    <t>CRUD Testing</t>
+  </si>
+  <si>
+    <t>Test thêm/xóa vé</t>
+  </si>
+  <si>
+    <t>“Phân tích testAddTicket và testRemoveTicket.”</t>
+  </si>
+  <si>
+    <t>AI giải thích cách thêm vé mới, kiểm tra tồn tại, sau đó xóa và xác nhận không còn.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Kiểm tra logic CRUD hoạt động đúng. Decision: Giữ test để xác nhận repository cập nhật file CSV.</t>
+  </si>
+  <si>
+    <t>Code TicketRepositoryTest + log console</t>
+  </si>
+  <si>
+    <t>🧠 HALLUCINATION DETECTION LOG (Phiên bản mở rộng)</t>
+  </si>
+  <si>
+    <t>AI’s Claim</t>
+  </si>
+  <si>
+    <t>AI nói file CSV sai vì thiếu header</t>
+  </si>
+  <si>
+    <t>Thực tế không bắt buộc, chỉ thiếu tiêu đề</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kiểm tra code </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>fromCsv()</t>
+    </r>
+  </si>
+  <si>
+    <t>Thêm header để dễ đọc, nhưng code vẫn chạy</t>
+  </si>
+  <si>
+    <t>AI nói synchronized đủ để ngăn double booking</t>
+  </si>
+  <si>
+    <t>Thực tế vẫn lỗi khi nhiều threads</t>
+  </si>
+  <si>
+    <t>Chạy simulator kiểm chứng</t>
+  </si>
+  <si>
+    <t>Thêm FileLock để đảm bảo atomic write</t>
+  </si>
+  <si>
+    <t>AI nói chỉ cần ticketType = VIP/NORMAL</t>
+  </si>
+  <si>
+    <t>Thực tế cần mapping từ sections.csv</t>
+  </si>
+  <si>
+    <t>Kiểm tra dữ liệu stadium</t>
+  </si>
+  <si>
+    <t>Bổ sung stadiumId và logic giá vé theo khu vực</t>
+  </si>
+  <si>
+    <t>AI dùng Thread.stop() để dừng simulator</t>
+  </si>
+  <si>
+    <t>Phương thức deprecated từ Java 8</t>
+  </si>
+  <si>
+    <t>Đọc tài liệu JavaDoc</t>
+  </si>
+  <si>
+    <t>AI nói có nghiên cứu về CSV Optimistic Locking</t>
+  </si>
+  <si>
+    <t>Không có paper nào</t>
+  </si>
+  <si>
+    <t>Tìm Google Scholar</t>
+  </si>
+  <si>
+    <t>Giữ version field, chứng minh bằng simulator</t>
+  </si>
+  <si>
+    <t>AI nói test CSV chỉ kiểm tra số cột</t>
+  </si>
+  <si>
+    <t>Thực tế còn kiểm tra ô trống và logic dữ liệu</t>
+  </si>
+  <si>
+    <t>Đọc lại code TicketCsvTest</t>
+  </si>
+  <si>
+    <t>Giữ test để đảm bảo dữ liệu sạch trước khi load</t>
+  </si>
+  <si>
+    <t>👉 Khi thầy hỏi, bạn có thể nói:</t>
+  </si>
+  <si>
+    <t>“Em viết AI log để ghi lại quá trình AI hỗ trợ em trong việc kiểm thử và phát triển hệ thống vé. Log này thể hiện rõ từng vấn đề, cách AI phản hồi, cách em phân tích lại và bằng chứng thực tế. Em cũng có bảng Hallucination Detection để chỉ ra các lỗi AI và cách em sửa lại cho đúng.”</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bạn có muốn mình viết thêm phần </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Self-Assessment Checklist</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (đánh giá mức độ chính xác và cải thiện sau khi sửa lỗi AI) để hoàn thiện file Excel không?</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -566,7 +742,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -642,6 +818,27 @@
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -696,7 +893,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -749,7 +946,24 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1053,7 +1267,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -1062,7 +1276,7 @@
     <col min="5" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1072,12 +1286,12 @@
       <c r="E1" s="19"/>
       <c r="F1" s="19"/>
     </row>
-    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="18">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1085,7 +1299,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1093,7 +1307,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -1101,7 +1315,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -1109,12 +1323,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="18">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -1122,7 +1336,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1130,7 +1344,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -1142,7 +1356,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
@@ -1150,12 +1364,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="18">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
         <v>16</v>
       </c>
@@ -1169,7 +1383,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17" s="7" t="s">
         <v>20</v>
       </c>
@@ -1183,7 +1397,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18" s="7" t="s">
         <v>24</v>
       </c>
@@ -1197,7 +1411,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19" s="7" t="s">
         <v>28</v>
       </c>
@@ -1211,7 +1425,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20" s="7" t="s">
         <v>31</v>
       </c>
@@ -1219,12 +1433,12 @@
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
     </row>
-    <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="18">
       <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4">
       <c r="A23" s="6" t="s">
         <v>33</v>
       </c>
@@ -1235,7 +1449,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4">
       <c r="A24" s="7" t="s">
         <v>36</v>
       </c>
@@ -1246,7 +1460,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4">
       <c r="A25" s="7" t="s">
         <v>38</v>
       </c>
@@ -1257,7 +1471,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4">
       <c r="A26" s="7" t="s">
         <v>39</v>
       </c>
@@ -1268,7 +1482,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4">
       <c r="A27" s="7" t="s">
         <v>40</v>
       </c>
@@ -1289,8 +1503,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
@@ -1301,7 +1515,7 @@
     <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" s="20" t="s">
         <v>41</v>
       </c>
@@ -1313,7 +1527,7 @@
       <c r="G1" s="19"/>
       <c r="H1" s="19"/>
     </row>
-    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="30" customHeight="1">
       <c r="A2" s="18" t="s">
         <v>42</v>
       </c>
@@ -1325,7 +1539,7 @@
       <c r="G2" s="19"/>
       <c r="H2" s="19"/>
     </row>
-    <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>43</v>
       </c>
@@ -1351,7 +1565,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="57.6" customHeight="1">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -1377,7 +1591,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="42.6" customHeight="1">
       <c r="A5" s="7">
         <v>2</v>
       </c>
@@ -1396,14 +1610,14 @@
       <c r="F5" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" t="s">
         <v>138</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="58.2" customHeight="1">
       <c r="A6" s="7">
         <v>3</v>
       </c>
@@ -1429,7 +1643,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="79.95" customHeight="1">
       <c r="A7" s="7">
         <v>4</v>
       </c>
@@ -1455,7 +1669,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="79.95" customHeight="1">
       <c r="A8" s="7">
         <v>5</v>
       </c>
@@ -1481,7 +1695,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="79.95" customHeight="1">
       <c r="A9" s="7">
         <v>6</v>
       </c>
@@ -1507,175 +1721,250 @@
         <v>134</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-    </row>
-    <row r="22" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-    </row>
-    <row r="23" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-    </row>
-    <row r="24" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-    </row>
-    <row r="25" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-    </row>
-    <row r="26" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
+    <row r="10" spans="1:8" ht="79.95" customHeight="1">
+      <c r="A10" s="24">
+        <v>7</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="79.95" customHeight="1">
+      <c r="A11" s="24">
+        <v>8</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="79.95" customHeight="1">
+      <c r="A12" s="24">
+        <v>9</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="79.95" customHeight="1"/>
+    <row r="14" spans="1:8" ht="79.95" customHeight="1"/>
+    <row r="15" spans="1:8" ht="79.95" customHeight="1">
+      <c r="A15" s="26" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="79.95" customHeight="1"/>
+    <row r="17" spans="1:6" ht="79.95" customHeight="1">
+      <c r="A17" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="79.95" customHeight="1">
+      <c r="A18" s="24">
+        <v>1</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="79.95" customHeight="1">
+      <c r="A19" s="24">
+        <v>2</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="79.95" customHeight="1">
+      <c r="A20" s="24">
+        <v>3</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="79.95" customHeight="1">
+      <c r="A21" s="24">
+        <v>4</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="79.95" customHeight="1">
+      <c r="A22" s="24">
+        <v>5</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="79.95" customHeight="1">
+      <c r="A23" s="24">
+        <v>6</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="79.95" customHeight="1"/>
+    <row r="25" spans="1:6" ht="79.95" customHeight="1">
+      <c r="A25" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="79.95" customHeight="1">
+      <c r="A26" s="27"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="27" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>221</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1690,14 +1979,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="22" t="s">
         <v>56</v>
       </c>
@@ -1707,7 +1996,7 @@
       <c r="E1" s="19"/>
       <c r="F1" s="19"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="21" t="s">
         <v>57</v>
       </c>
@@ -1717,7 +2006,7 @@
       <c r="E2" s="19"/>
       <c r="F2" s="19"/>
     </row>
-    <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>58</v>
       </c>
@@ -1737,7 +2026,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="60" customHeight="1">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -1757,7 +2046,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="62.4" customHeight="1">
       <c r="A5" s="7">
         <v>2</v>
       </c>
@@ -1777,7 +2066,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="60" customHeight="1">
       <c r="A6" s="7">
         <v>3</v>
       </c>
@@ -1797,7 +2086,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="60" customHeight="1">
       <c r="A7" s="7">
         <v>4</v>
       </c>
@@ -1817,7 +2106,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="60" customHeight="1">
       <c r="A8" s="7">
         <v>5</v>
       </c>
@@ -1837,7 +2126,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="60" customHeight="1">
       <c r="A9" s="7">
         <v>6</v>
       </c>
@@ -1857,31 +2146,55 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
+    <row r="10" spans="1:6" ht="60" customHeight="1">
+      <c r="A10" s="28">
+        <v>7</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="60" customHeight="1">
+      <c r="A11" s="28">
+        <v>8</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="60" customHeight="1">
+      <c r="A12" s="29"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="60" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -1889,7 +2202,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="60" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -1897,7 +2210,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="60" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -1905,7 +2218,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="60" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -1913,7 +2226,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
     </row>
-    <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="60" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1921,7 +2234,7 @@
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="60" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1929,7 +2242,7 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="60" customHeight="1">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1937,7 +2250,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="60" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1945,7 +2258,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="60" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -1953,7 +2266,7 @@
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="60" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1961,7 +2274,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="60" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -1969,7 +2282,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="60" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -1977,12 +2290,12 @@
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="18">
       <c r="A30" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
       <c r="A31" s="10" t="s">
         <v>66</v>
       </c>
@@ -1993,7 +2306,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="28.8">
       <c r="A32" s="7" t="s">
         <v>64</v>
       </c>
@@ -2004,7 +2317,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="28.8">
       <c r="A33" s="7" t="s">
         <v>71</v>
       </c>
@@ -2015,7 +2328,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="28.8">
       <c r="A34" s="7" t="s">
         <v>74</v>
       </c>
@@ -2026,7 +2339,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="28.8">
       <c r="A35" s="7" t="s">
         <v>77</v>
       </c>
@@ -2037,7 +2350,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="43.2">
       <c r="A36" s="7" t="s">
         <v>80</v>
       </c>
@@ -2060,7 +2373,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
@@ -2068,7 +2381,7 @@
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="20" t="s">
         <v>83</v>
       </c>
@@ -2076,7 +2389,7 @@
       <c r="C1" s="19"/>
       <c r="D1" s="19"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" s="23" t="s">
         <v>84</v>
       </c>
@@ -2084,12 +2397,12 @@
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
     </row>
-    <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="18">
       <c r="A4" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
         <v>86</v>
       </c>
@@ -2103,7 +2416,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" s="12" t="s">
         <v>90</v>
       </c>
@@ -2115,7 +2428,7 @@
       </c>
       <c r="D6" s="13"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" s="12" t="s">
         <v>93</v>
       </c>
@@ -2127,7 +2440,7 @@
       </c>
       <c r="D7" s="13"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" s="12" t="s">
         <v>95</v>
       </c>
@@ -2139,7 +2452,7 @@
       </c>
       <c r="D8" s="13"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" s="12" t="s">
         <v>97</v>
       </c>
@@ -2151,7 +2464,7 @@
       </c>
       <c r="D9" s="13"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
         <v>99</v>
       </c>
@@ -2163,12 +2476,12 @@
       </c>
       <c r="D10" s="13"/>
     </row>
-    <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="18">
       <c r="A12" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
         <v>86</v>
       </c>
@@ -2182,7 +2495,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" s="12" t="s">
         <v>90</v>
       </c>
@@ -2194,7 +2507,7 @@
       </c>
       <c r="D14" s="13"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">
         <v>93</v>
       </c>
@@ -2206,7 +2519,7 @@
       </c>
       <c r="D15" s="13"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" s="12" t="s">
         <v>95</v>
       </c>
@@ -2218,7 +2531,7 @@
       </c>
       <c r="D16" s="13"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17" s="12" t="s">
         <v>97</v>
       </c>
@@ -2230,7 +2543,7 @@
       </c>
       <c r="D17" s="13"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18" s="12" t="s">
         <v>99</v>
       </c>
@@ -2242,32 +2555,32 @@
       </c>
       <c r="D18" s="13"/>
     </row>
-    <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15.6">
       <c r="A20" s="14" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21" s="15" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22" s="15" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" ht="18">
       <c r="A25" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4">
       <c r="A26" s="16" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="43.2">
       <c r="A27" s="17" t="s">
         <v>43</v>
       </c>
@@ -2281,7 +2594,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4">
       <c r="A28" s="9" t="s">
         <v>51</v>
       </c>
@@ -2289,7 +2602,7 @@
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4">
       <c r="A29" s="9" t="s">
         <v>53</v>
       </c>
@@ -2297,7 +2610,7 @@
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4">
       <c r="A30" s="9" t="s">
         <v>55</v>
       </c>
